--- a/leads/sabusinessdirectories_contacts (3).xlsx
+++ b/leads/sabusinessdirectories_contacts (3).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manu\Documents\Web dev\Projects\unlimited_webscraper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manu\Documents\Web dev\Projects\unlimited_webscraper\leads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="143">
   <si>
     <t>Name</t>
   </si>
@@ -198,15 +198,9 @@
     <t>ORION HOTEL (Katse LodgeKatse Dam, LESOTHO)</t>
   </si>
   <si>
-    <t>Hotel +266 2891 0202 Toll free 086 199 1199 Central Reservations +27 (0)11 403 1218</t>
-  </si>
-  <si>
     <t>ORION HOTEL (Mohale LodgeMohale Dam, LESOTHO)</t>
   </si>
   <si>
-    <t>Hotel +266 2293 6432 Toll free 086 199 1199 Central Reservations +27 (0)11 403 1218</t>
-  </si>
-  <si>
     <t>Motor car service</t>
   </si>
   <si>
@@ -243,9 +237,6 @@
     <t>PROPSHAFTS</t>
   </si>
   <si>
-    <t>/Fax : 031 579 5585 Cell       : 082 371 8892  Contact Seelan Perumal</t>
-  </si>
-  <si>
     <t>KITCHEN CUPBOARDS</t>
   </si>
   <si>
@@ -255,9 +246,6 @@
     <t>Holmbush Pallets CC</t>
   </si>
   <si>
-    <t>032 4861265   Fax: 032 4861265   Cellular: 082 6719702   Email: holmbushpallets@telkomsa.net</t>
-  </si>
-  <si>
     <t>fertilizers</t>
   </si>
   <si>
@@ -282,60 +270,33 @@
     <t>032 533 4677</t>
   </si>
   <si>
-    <t>031 5794597   Category: motor car parts &amp; accessories – wh’sale &amp; mfrs   Keywords: motor components | spare parts | engine parts&amp;nb</t>
-  </si>
-  <si>
     <t>Griptite Fasteners</t>
   </si>
   <si>
-    <t>031 3124402   Category: bolts, nuts &amp; rivets</t>
-  </si>
-  <si>
     <t>Uni Brick 'N Block (PTY) LTD</t>
   </si>
   <si>
-    <t>032 5338658   Fax: 032 5338902   Category: brick mfrs &amp; suppliers</t>
-  </si>
-  <si>
     <t>J L Thusi Building</t>
   </si>
   <si>
-    <t>035 796 3196 072 326 9117     Category: building maintenance</t>
-  </si>
-  <si>
     <t>department of labour</t>
   </si>
   <si>
-    <t>NO: DUNDEE  034 212 3147 DURBAN 031 336 1500 ESTCOURT 036 352 2161 KOKSTAD 039 727 2140</t>
-  </si>
-  <si>
     <t>Exquisite Functions</t>
   </si>
   <si>
     <t>Mphazimas Plumbing</t>
   </si>
   <si>
-    <t>076 6361675   Fax: 035 7965512   Email: 0357965512@efg.co.za   Category: plumbers &amp; sanitary engineers   Keywords: plumbers | burst | leaks | installations | taps | toilets</t>
-  </si>
-  <si>
     <t>Kwa-Gijima Express Services</t>
   </si>
   <si>
-    <t>035 7721801   Fax: 035 7723718   Cellular: 082 4962777   Email: ria@kwagijima.co.za   Category: courier service   Keywords:</t>
-  </si>
-  <si>
     <t>Express Employment Professionals</t>
   </si>
   <si>
-    <t>035 7898188   Fax: 035 7898142   Email: reception@expressrbay.co.za   Homepage: http://www.expresspros.co.</t>
-  </si>
-  <si>
     <t>INTERNATIONAL SLABS SALES-HEAD OFFICE</t>
   </si>
   <si>
-    <t>034-995 1644 FAX:034-995 1476 EMAIL:erich@autobahn.co.za</t>
-  </si>
-  <si>
     <t>Inkanyezi Cash &amp; Carry</t>
   </si>
   <si>
@@ -423,15 +384,9 @@
     <t>NEWPARK</t>
   </si>
   <si>
-    <t>031-940 1493 WEBSITE:WWW.NEWPARKTECHNOLOGIES.CO.ZA</t>
-  </si>
-  <si>
     <t>LABOUR LAW MANAGEMENT CONSULTING</t>
   </si>
   <si>
-    <t>No. : 011 888 7944 Fax No. : 011 782 0664 Cellular No. : 082 8522 973 E-Mail Add. ivan@labourlawadvice.co.za Website Add. : www.labourlawadvice.co.za TRADE HEADINGS 1) LABOUR LAW CONSULTANTS</t>
-  </si>
-  <si>
     <t>ASSESSANDBEYOND.COM</t>
   </si>
   <si>
@@ -441,27 +396,15 @@
     <t>Metro Agencies CC</t>
   </si>
   <si>
-    <t>031 4095242 CELL:   084 4043053 FAX:      031 4097209 WEDSITE:www.metroagencies. co.za</t>
-  </si>
-  <si>
     <t>New Creation Steelworks</t>
   </si>
   <si>
-    <t>031 401 2514 Mobile: 084 738 8933   Email: newcreation@telkomsa.net</t>
-  </si>
-  <si>
     <t>Trellidor</t>
   </si>
   <si>
-    <t>031 2017927  Email : alvin@trellidorbedfordview.co.za Website addresses:www.trellidor.co.za</t>
-  </si>
-  <si>
     <t>Kajees Burglar Guards &amp; Gates</t>
   </si>
   <si>
-    <t>Numbers :031 4039046  WEBSITE : www.kajees.co.za</t>
-  </si>
-  <si>
     <t>J R Burglar Guards Gates &amp; Automation</t>
   </si>
   <si>
@@ -495,7 +438,16 @@
     <t>Coroma:Redhill</t>
   </si>
   <si>
-    <t>031 5695000 Email : info@trellidorsoweto.co.za Website addresses:www.trellidor.co.za</t>
+    <t>031-940 1493</t>
+  </si>
+  <si>
+    <t>Hotel +266 2891 0202</t>
+  </si>
+  <si>
+    <t>Hotel +266 2293 6432</t>
+  </si>
+  <si>
+    <t>034-995 1644</t>
   </si>
 </sst>
 </file>
@@ -551,11 +503,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -860,6 +813,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1098,36 +1055,36 @@
         <v>58</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s">
         <v>3</v>
@@ -1135,127 +1092,127 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>73</v>
-      </c>
-      <c r="B38" t="s">
-        <v>74</v>
+        <v>71</v>
+      </c>
+      <c r="B38" s="2">
+        <v>315795585</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>77</v>
-      </c>
-      <c r="B40" t="s">
-        <v>78</v>
+        <v>74</v>
+      </c>
+      <c r="B40" s="2">
+        <v>324861265</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B43" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>85</v>
-      </c>
-      <c r="B45" t="s">
-        <v>87</v>
+        <v>81</v>
+      </c>
+      <c r="B45" s="2">
+        <v>315794597</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>88</v>
-      </c>
-      <c r="B46" t="s">
-        <v>89</v>
+        <v>83</v>
+      </c>
+      <c r="B46" s="2">
+        <v>313124402</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>90</v>
-      </c>
-      <c r="B47" t="s">
-        <v>91</v>
+        <v>84</v>
+      </c>
+      <c r="B47" s="2">
+        <v>325338658</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>92</v>
-      </c>
-      <c r="B48" t="s">
-        <v>93</v>
+        <v>85</v>
+      </c>
+      <c r="B48" s="2">
+        <v>3.5796319607232599E+18</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>94</v>
-      </c>
-      <c r="B49" t="s">
-        <v>95</v>
+        <v>86</v>
+      </c>
+      <c r="B49" s="2">
+        <v>342123147</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B50" t="s">
         <v>3</v>
@@ -1263,39 +1220,39 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>97</v>
-      </c>
-      <c r="B51" t="s">
-        <v>98</v>
+        <v>88</v>
+      </c>
+      <c r="B51" s="2">
+        <v>766361675</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>99</v>
-      </c>
-      <c r="B52" t="s">
-        <v>100</v>
+        <v>89</v>
+      </c>
+      <c r="B52" s="2">
+        <v>357721801</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>101</v>
-      </c>
-      <c r="B53" t="s">
-        <v>102</v>
+        <v>90</v>
+      </c>
+      <c r="B53" s="2">
+        <v>357898188</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B55" t="s">
         <v>3</v>
@@ -1303,7 +1260,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B56" t="s">
         <v>3</v>
@@ -1311,210 +1268,210 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B57" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B58" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B59" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="B60" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="B61" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="B62" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="B63" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="B64" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B66" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B67" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B68" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="B69" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B70" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>135</v>
-      </c>
-      <c r="B71" t="s">
-        <v>136</v>
+        <v>121</v>
+      </c>
+      <c r="B71" s="2">
+        <v>118887944</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="B72" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>139</v>
-      </c>
-      <c r="B73" t="s">
-        <v>140</v>
+        <v>124</v>
+      </c>
+      <c r="B73" s="2">
+        <v>314095242</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>141</v>
-      </c>
-      <c r="B74" t="s">
-        <v>142</v>
+        <v>125</v>
+      </c>
+      <c r="B74" s="2">
+        <v>314012514</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>143</v>
-      </c>
-      <c r="B75" t="s">
-        <v>144</v>
+        <v>126</v>
+      </c>
+      <c r="B75" s="2">
+        <v>312017927</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>145</v>
-      </c>
-      <c r="B76" t="s">
-        <v>146</v>
+        <v>127</v>
+      </c>
+      <c r="B76" s="2">
+        <v>314039046</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="B78" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="B79" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="B80" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="B81" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>157</v>
-      </c>
-      <c r="B82" t="s">
-        <v>158</v>
+        <v>138</v>
+      </c>
+      <c r="B82" s="2">
+        <v>315695000</v>
       </c>
     </row>
   </sheetData>
